--- a/diseases/d039/2005-2009.xlsx
+++ b/diseases/d039/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>85</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>28.63548543043346</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>73</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.1525548422118998</v>
       </c>
@@ -2001,9 +1992,6 @@
       <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.1081519768883552</v>
       </c>
@@ -2545,9 +2533,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -3089,9 +3074,6 @@
       <c r="O15" t="n">
         <v>49</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.1023998255942889</v>
       </c>
@@ -3237,9 +3219,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -3781,9 +3760,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4325,9 +4301,6 @@
       <c r="O22" t="n">
         <v>116</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.2424159136517859</v>
       </c>
@@ -4473,9 +4446,6 @@
       <c r="O23" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -5017,9 +4987,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5561,9 +5528,6 @@
       <c r="O29" t="n">
         <v>195</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.4075095100180884</v>
       </c>
@@ -5709,9 +5673,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6253,9 +6214,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6797,9 +6755,6 @@
       <c r="O36" t="n">
         <v>238</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.4973705814579745</v>
       </c>
@@ -6945,9 +6900,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7489,9 +7441,6 @@
       <c r="O40" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -8033,9 +7982,6 @@
       <c r="O43" t="n">
         <v>191</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.3991503405818199</v>
       </c>
@@ -8181,9 +8127,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8725,9 +8668,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -9269,9 +9209,6 @@
       <c r="O50" t="n">
         <v>153</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.3197382309372694</v>
       </c>
@@ -9417,9 +9354,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -9961,9 +9895,6 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -10505,9 +10436,6 @@
       <c r="O57" t="n">
         <v>94</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.1964404817523093</v>
       </c>
@@ -10653,9 +10581,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -11197,9 +11122,6 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -11741,9 +11663,6 @@
       <c r="O64" t="n">
         <v>76</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.1588242192891011</v>
       </c>
@@ -11889,9 +11808,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12433,9 +12349,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12977,9 +12890,6 @@
       <c r="O71" t="n">
         <v>179</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.3740728322730145</v>
       </c>
@@ -13125,9 +13035,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13669,9 +13576,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -14213,9 +14117,6 @@
       <c r="O78" t="n">
         <v>259</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.5412562209983841</v>
       </c>
@@ -14361,9 +14262,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -14905,9 +14803,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -15449,9 +15344,6 @@
       <c r="O85" t="n">
         <v>240</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.5015501661761088</v>
       </c>
@@ -15597,9 +15489,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16141,9 +16030,6 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -16685,9 +16571,6 @@
       <c r="O92" t="n">
         <v>29</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>9.543429184464614</v>
       </c>
@@ -17081,9 +16964,6 @@
       <c r="O94" t="n">
         <v>89</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.185391493977875</v>
       </c>
@@ -17229,9 +17109,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -17773,9 +17650,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -18317,9 +18191,6 @@
       <c r="O101" t="n">
         <v>65</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.1353982821186727</v>
       </c>
@@ -18465,9 +18336,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -19009,9 +18877,6 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -19553,9 +19418,6 @@
       <c r="O108" t="n">
         <v>147</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.3062084226376137</v>
       </c>
@@ -19701,9 +19563,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -20245,9 +20104,6 @@
       <c r="O112" t="n">
         <v>2</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -20789,9 +20645,6 @@
       <c r="O115" t="n">
         <v>177</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.3686999374616166</v>
       </c>
@@ -20937,9 +20790,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -21481,9 +21331,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -22025,9 +21872,6 @@
       <c r="O122" t="n">
         <v>287</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.5978354918162935</v>
       </c>
@@ -22173,9 +22017,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22717,9 +22558,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -23261,9 +23099,6 @@
       <c r="O129" t="n">
         <v>264</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.5499253304512247</v>
       </c>
@@ -23409,9 +23244,6 @@
       <c r="O130" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -24101,9 +23933,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -24645,9 +24474,6 @@
       <c r="O137" t="n">
         <v>192</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.399945694873618</v>
       </c>
@@ -24793,9 +24619,6 @@
       <c r="O138" t="n">
         <v>8</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.1716556227730365</v>
       </c>
@@ -25485,9 +25308,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -26029,9 +25849,6 @@
       <c r="O145" t="n">
         <v>163</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.3395372305437486</v>
       </c>
@@ -26177,9 +25994,6 @@
       <c r="O146" t="n">
         <v>10</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.2145695284662957</v>
       </c>
@@ -26869,9 +26683,6 @@
       <c r="O150" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -27413,9 +27224,6 @@
       <c r="O153" t="n">
         <v>234</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.4874338156272219</v>
       </c>
@@ -27561,9 +27369,6 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -28105,9 +27910,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -28649,9 +28451,6 @@
       <c r="O160" t="n">
         <v>122</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.2541321602842781</v>
       </c>
@@ -28797,9 +28596,6 @@
       <c r="O161" t="n">
         <v>1</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -29341,9 +29137,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -29885,9 +29678,6 @@
       <c r="O167" t="n">
         <v>121</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.2520491097901447</v>
       </c>
@@ -30033,9 +29823,6 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -30725,9 +30512,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -31269,9 +31053,6 @@
       <c r="O175" t="n">
         <v>228</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.4749355126624213</v>
       </c>
@@ -31417,9 +31198,6 @@
       <c r="O176" t="n">
         <v>2</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.04291390569325913</v>
       </c>
@@ -32109,9 +31887,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -32653,9 +32428,6 @@
       <c r="O183" t="n">
         <v>1</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.3208722591492714</v>
       </c>
@@ -33049,9 +32821,6 @@
       <c r="O185" t="n">
         <v>133</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.2760589332686373</v>
       </c>
@@ -33197,9 +32966,6 @@
       <c r="O186" t="n">
         <v>2</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -33741,9 +33507,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -34285,9 +34048,6 @@
       <c r="O192" t="n">
         <v>88</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.1826555347942863</v>
       </c>
@@ -34433,9 +34193,6 @@
       <c r="O193" t="n">
         <v>2</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -34977,9 +34734,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -35521,9 +35275,6 @@
       <c r="O199" t="n">
         <v>163</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.3383278655848713</v>
       </c>
@@ -35669,9 +35420,6 @@
       <c r="O200" t="n">
         <v>3</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.06370765829760396</v>
       </c>
@@ -36213,9 +35961,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -36757,9 +36502,6 @@
       <c r="O206" t="n">
         <v>494</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>1.025361752140653</v>
       </c>
@@ -36905,9 +36647,6 @@
       <c r="O207" t="n">
         <v>2</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -37449,9 +37188,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -37993,9 +37729,6 @@
       <c r="O213" t="n">
         <v>677</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>1.40520223926968</v>
       </c>
@@ -38141,9 +37874,6 @@
       <c r="O214" t="n">
         <v>2</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -38833,9 +38563,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -39377,9 +39104,6 @@
       <c r="O221" t="n">
         <v>752</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>1.560874570060265</v>
       </c>
@@ -39525,9 +39249,6 @@
       <c r="O222" t="n">
         <v>1</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -40069,9 +39790,6 @@
       <c r="O225" t="n">
         <v>2</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -40613,9 +40331,6 @@
       <c r="O228" t="n">
         <v>484</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>1.004605441368575</v>
       </c>
@@ -40761,9 +40476,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -41305,9 +41017,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -41849,9 +41558,6 @@
       <c r="O235" t="n">
         <v>228</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.4732438856033782</v>
       </c>
@@ -41997,9 +41703,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -42689,9 +42392,6 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -43233,9 +42933,6 @@
       <c r="O243" t="n">
         <v>256</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.5313615557651966</v>
       </c>
@@ -43381,9 +43078,6 @@
       <c r="O244" t="n">
         <v>3</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.06370765829760396</v>
       </c>
@@ -44073,9 +43767,6 @@
       <c r="O248" t="n">
         <v>1</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -44617,9 +44308,6 @@
       <c r="O251" t="n">
         <v>364</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.7555297121036388</v>
       </c>
@@ -44765,9 +44453,6 @@
       <c r="O252" t="n">
         <v>2</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -45457,9 +45142,6 @@
       <c r="O256" t="n">
         <v>2</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -46001,9 +45683,6 @@
       <c r="O259" t="n">
         <v>411</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.8530843727324054</v>
       </c>
@@ -46149,9 +45828,6 @@
       <c r="O260" t="n">
         <v>1</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -46841,9 +46517,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0</v>
       </c>
@@ -47385,9 +47058,6 @@
       <c r="O267" t="n">
         <v>507</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>1.052344956144354</v>
       </c>
@@ -47533,9 +47203,6 @@
       <c r="O268" t="n">
         <v>5</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.1061794304960066</v>
       </c>
@@ -48225,9 +47892,6 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0</v>
       </c>
@@ -48769,9 +48433,6 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -49165,9 +48826,6 @@
       <c r="O277" t="n">
         <v>233</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.4818380853218615</v>
       </c>
@@ -49313,9 +48971,6 @@
       <c r="O278" t="n">
         <v>1</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -50005,9 +49660,6 @@
       <c r="O282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0</v>
       </c>
@@ -50549,9 +50201,6 @@
       <c r="O285" t="n">
         <v>109</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.2254092330475661</v>
       </c>
@@ -50697,9 +50346,6 @@
       <c r="O286" t="n">
         <v>1</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -51389,9 +51035,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -51933,9 +51576,6 @@
       <c r="O293" t="n">
         <v>211</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.4363426437893252</v>
       </c>
@@ -52081,9 +51721,6 @@
       <c r="O294" t="n">
         <v>1</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -52625,9 +52262,6 @@
       <c r="O297" t="n">
         <v>0</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0</v>
       </c>
@@ -53169,9 +52803,6 @@
       <c r="O300" t="n">
         <v>486</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>1.005035662946029</v>
       </c>
@@ -53317,9 +52948,6 @@
       <c r="O301" t="n">
         <v>1</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -54009,9 +53637,6 @@
       <c r="O305" t="n">
         <v>2</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -54553,9 +54178,6 @@
       <c r="O308" t="n">
         <v>654</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>1.352455398285397</v>
       </c>
@@ -54701,9 +54323,6 @@
       <c r="O309" t="n">
         <v>1</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -55393,9 +55012,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -55937,9 +55553,6 @@
       <c r="O316" t="n">
         <v>760</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>1.571660707487617</v>
       </c>
@@ -56085,9 +55698,6 @@
       <c r="O317" t="n">
         <v>1</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -56629,9 +56239,6 @@
       <c r="O320" t="n">
         <v>1</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -57173,9 +56780,6 @@
       <c r="O323" t="n">
         <v>432</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0.8933650337298034</v>
       </c>
@@ -57321,9 +56925,6 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0</v>
       </c>
@@ -57865,9 +57466,6 @@
       <c r="O327" t="n">
         <v>0</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0</v>
       </c>
@@ -58409,9 +58007,6 @@
       <c r="O330" t="n">
         <v>217</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0.4487504914800169</v>
       </c>
@@ -58557,9 +58152,6 @@
       <c r="O331" t="n">
         <v>5</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0.1048635504994546</v>
       </c>
@@ -59101,9 +58693,6 @@
       <c r="O334" t="n">
         <v>0</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0</v>
       </c>
@@ -59645,9 +59234,6 @@
       <c r="O337" t="n">
         <v>319</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0.6596839022217761</v>
       </c>
@@ -59793,9 +59379,6 @@
       <c r="O338" t="n">
         <v>2</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -60337,9 +59920,6 @@
       <c r="O341" t="n">
         <v>1</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -60881,9 +60461,6 @@
       <c r="O344" t="n">
         <v>344</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.7113832675996582</v>
       </c>
@@ -61029,9 +60606,6 @@
       <c r="O345" t="n">
         <v>3</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0.06291813029967276</v>
       </c>
@@ -61573,9 +61147,6 @@
       <c r="O348" t="n">
         <v>1</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -62117,9 +61688,6 @@
       <c r="O351" t="n">
         <v>376</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0.7775584552833473</v>
       </c>
@@ -62265,9 +61833,6 @@
       <c r="O352" t="n">
         <v>0</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0</v>
       </c>
@@ -62809,9 +62374,6 @@
       <c r="O355" t="n">
         <v>0</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0</v>
       </c>
@@ -63353,9 +62915,6 @@
       <c r="O358" t="n">
         <v>401</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0.8292578206612295</v>
       </c>
@@ -63501,9 +63060,6 @@
       <c r="O359" t="n">
         <v>0</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0</v>
       </c>
@@ -64045,9 +63601,6 @@
       <c r="O362" t="n">
         <v>0</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0</v>
       </c>
@@ -64589,9 +64142,6 @@
       <c r="O365" t="n">
         <v>4</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>1.255445494833842</v>
       </c>
@@ -64985,9 +64535,6 @@
       <c r="O367" t="n">
         <v>210</v>
       </c>
-      <c r="Q367" t="n">
-        <v>0</v>
-      </c>
       <c r="R367" t="n">
         <v>0.4325732921030563</v>
       </c>
@@ -65133,9 +64680,6 @@
       <c r="O368" t="n">
         <v>1</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -65677,9 +65221,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -66221,9 +65762,6 @@
       <c r="O374" t="n">
         <v>197</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0.4057949454490576</v>
       </c>
@@ -66369,9 +65907,6 @@
       <c r="O375" t="n">
         <v>1</v>
       </c>
-      <c r="Q375" t="n">
-        <v>0</v>
-      </c>
       <c r="R375" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -66913,9 +66448,6 @@
       <c r="O378" t="n">
         <v>0</v>
       </c>
-      <c r="Q378" t="n">
-        <v>0</v>
-      </c>
       <c r="R378" t="n">
         <v>0</v>
       </c>
@@ -67457,9 +66989,6 @@
       <c r="O381" t="n">
         <v>363</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0.7477338334924258</v>
       </c>
@@ -67605,9 +67134,6 @@
       <c r="O382" t="n">
         <v>3</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0.06212952037563508</v>
       </c>
@@ -68149,9 +67675,6 @@
       <c r="O385" t="n">
         <v>1</v>
       </c>
-      <c r="Q385" t="n">
-        <v>0</v>
-      </c>
       <c r="R385" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -68693,9 +68216,6 @@
       <c r="O388" t="n">
         <v>537</v>
       </c>
-      <c r="Q388" t="n">
-        <v>0</v>
-      </c>
       <c r="R388" t="n">
         <v>1.106151704092101</v>
       </c>
@@ -68841,9 +68361,6 @@
       <c r="O389" t="n">
         <v>0</v>
       </c>
-      <c r="Q389" t="n">
-        <v>0</v>
-      </c>
       <c r="R389" t="n">
         <v>0</v>
       </c>
@@ -69385,9 +68902,6 @@
       <c r="O392" t="n">
         <v>0</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0</v>
       </c>
@@ -69929,9 +69443,6 @@
       <c r="O395" t="n">
         <v>772</v>
       </c>
-      <c r="Q395" t="n">
-        <v>0</v>
-      </c>
       <c r="R395" t="n">
         <v>1.590221816683616</v>
       </c>
@@ -70077,9 +69588,6 @@
       <c r="O396" t="n">
         <v>1</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -70769,9 +70277,6 @@
       <c r="O400" t="n">
         <v>0</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0</v>
       </c>
@@ -71313,9 +70818,6 @@
       <c r="O403" t="n">
         <v>1324</v>
       </c>
-      <c r="Q403" t="n">
-        <v>0</v>
-      </c>
       <c r="R403" t="n">
         <v>2.727271613068793</v>
       </c>
@@ -71461,9 +70963,6 @@
       <c r="O404" t="n">
         <v>0</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0</v>
       </c>
@@ -72153,9 +71652,6 @@
       <c r="O408" t="n">
         <v>0</v>
       </c>
-      <c r="Q408" t="n">
-        <v>0</v>
-      </c>
       <c r="R408" t="n">
         <v>0</v>
       </c>
@@ -72697,9 +72193,6 @@
       <c r="O411" t="n">
         <v>894</v>
       </c>
-      <c r="Q411" t="n">
-        <v>0</v>
-      </c>
       <c r="R411" t="n">
         <v>1.841526300667297</v>
       </c>
@@ -72845,9 +72338,6 @@
       <c r="O412" t="n">
         <v>0</v>
       </c>
-      <c r="Q412" t="n">
-        <v>0</v>
-      </c>
       <c r="R412" t="n">
         <v>0</v>
       </c>
@@ -73389,9 +72879,6 @@
       <c r="O415" t="n">
         <v>0</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0</v>
       </c>
@@ -73933,9 +73420,6 @@
       <c r="O418" t="n">
         <v>486</v>
       </c>
-      <c r="Q418" t="n">
-        <v>0</v>
-      </c>
       <c r="R418" t="n">
         <v>1.001098190295645</v>
       </c>
@@ -74081,9 +73565,6 @@
       <c r="O419" t="n">
         <v>3</v>
       </c>
-      <c r="Q419" t="n">
-        <v>0</v>
-      </c>
       <c r="R419" t="n">
         <v>0.06212952037563508</v>
       </c>
@@ -74773,9 +74254,6 @@
       <c r="O423" t="n">
         <v>0</v>
       </c>
-      <c r="Q423" t="n">
-        <v>0</v>
-      </c>
       <c r="R423" t="n">
         <v>0</v>
       </c>
@@ -75317,9 +74795,6 @@
       <c r="O426" t="n">
         <v>528</v>
       </c>
-      <c r="Q426" t="n">
-        <v>0</v>
-      </c>
       <c r="R426" t="n">
         <v>1.087612848716256</v>
       </c>
@@ -75465,9 +74940,6 @@
       <c r="O427" t="n">
         <v>1</v>
       </c>
-      <c r="Q427" t="n">
-        <v>0</v>
-      </c>
       <c r="R427" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -76009,9 +75481,6 @@
       <c r="O430" t="n">
         <v>0</v>
       </c>
-      <c r="Q430" t="n">
-        <v>0</v>
-      </c>
       <c r="R430" t="n">
         <v>0</v>
       </c>
@@ -76553,9 +76022,6 @@
       <c r="O433" t="n">
         <v>425</v>
       </c>
-      <c r="Q433" t="n">
-        <v>0</v>
-      </c>
       <c r="R433" t="n">
         <v>0.8754459483038045</v>
       </c>
@@ -76701,9 +76167,6 @@
       <c r="O434" t="n">
         <v>1</v>
       </c>
-      <c r="Q434" t="n">
-        <v>0</v>
-      </c>
       <c r="R434" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -77245,9 +76708,6 @@
       <c r="O437" t="n">
         <v>0</v>
       </c>
-      <c r="Q437" t="n">
-        <v>0</v>
-      </c>
       <c r="R437" t="n">
         <v>0</v>
       </c>
@@ -77789,9 +77249,6 @@
       <c r="O440" t="n">
         <v>341</v>
       </c>
-      <c r="Q440" t="n">
-        <v>0</v>
-      </c>
       <c r="R440" t="n">
         <v>0.7024166314625819</v>
       </c>
@@ -77937,9 +77394,6 @@
       <c r="O441" t="n">
         <v>1</v>
       </c>
-      <c r="Q441" t="n">
-        <v>0</v>
-      </c>
       <c r="R441" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -78481,9 +77935,6 @@
       <c r="O444" t="n">
         <v>0</v>
       </c>
-      <c r="Q444" t="n">
-        <v>0</v>
-      </c>
       <c r="R444" t="n">
         <v>0</v>
       </c>
@@ -79025,9 +78476,6 @@
       <c r="O447" t="n">
         <v>322</v>
       </c>
-      <c r="Q447" t="n">
-        <v>0</v>
-      </c>
       <c r="R447" t="n">
         <v>0.6632790478913529</v>
       </c>
@@ -79171,9 +78619,6 @@
         <v>0</v>
       </c>
       <c r="O448" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q448" t="n">
         <v>0</v>
       </c>
       <c r="R448" t="n">
